--- a/data/viviate.xlsx
+++ b/data/viviate.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,30 +457,55 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -505,21 +530,36 @@
         <v>32</v>
       </c>
       <c r="F2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H2" t="n">
+        <v>28</v>
+      </c>
+      <c r="I2" t="n">
+        <v>31</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K2" t="n">
         <v>14</v>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>21</v>
       </c>
-      <c r="H2" t="n">
+      <c r="M2" t="n">
         <v>21</v>
       </c>
-      <c r="I2" t="n">
+      <c r="N2" t="n">
         <v>21</v>
       </c>
-      <c r="J2" t="n">
+      <c r="O2" t="n">
         <v>20</v>
       </c>
-      <c r="K2" t="n">
+      <c r="P2" t="n">
         <v>20</v>
       </c>
     </row>
@@ -542,21 +582,36 @@
         <v>37</v>
       </c>
       <c r="F3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" t="n">
+        <v>22</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
         <v>13</v>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>22</v>
       </c>
-      <c r="H3" t="n">
+      <c r="M3" t="n">
         <v>24</v>
       </c>
-      <c r="I3" t="n">
+      <c r="N3" t="n">
         <v>28</v>
       </c>
-      <c r="J3" t="n">
+      <c r="O3" t="n">
         <v>18</v>
       </c>
-      <c r="K3" t="n">
+      <c r="P3" t="n">
         <v>16</v>
       </c>
     </row>
@@ -579,21 +634,36 @@
         <v>35</v>
       </c>
       <c r="F4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>12</v>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>22</v>
       </c>
-      <c r="H4" t="n">
+      <c r="M4" t="n">
         <v>23</v>
       </c>
-      <c r="I4" t="n">
+      <c r="N4" t="n">
         <v>26</v>
       </c>
-      <c r="J4" t="n">
+      <c r="O4" t="n">
         <v>18</v>
       </c>
-      <c r="K4" t="n">
+      <c r="P4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -607,7 +677,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
@@ -616,21 +686,36 @@
         <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
         <v>10</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>17</v>
+      </c>
+      <c r="M5" t="n">
+        <v>17</v>
+      </c>
+      <c r="N5" t="n">
+        <v>12</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -653,21 +738,36 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
+        <v>30</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>16</v>
       </c>
-      <c r="H6" t="n">
+      <c r="M6" t="n">
         <v>14</v>
       </c>
-      <c r="I6" t="n">
+      <c r="N6" t="n">
         <v>14</v>
       </c>
-      <c r="J6" t="n">
+      <c r="O6" t="n">
         <v>11</v>
       </c>
-      <c r="K6" t="n">
+      <c r="P6" t="n">
         <v>9</v>
       </c>
     </row>
@@ -690,23 +790,38 @@
         <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J7" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
+      <c r="L7" t="n">
+        <v>15</v>
+      </c>
+      <c r="M7" t="n">
+        <v>12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O7" t="n">
+        <v>13</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -727,23 +842,38 @@
         <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
         <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
         <v>10</v>
       </c>
+      <c r="L8" t="n">
+        <v>20</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -764,21 +894,36 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="n">
+        <v>13</v>
+      </c>
+      <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
+      <c r="L9" t="n">
         <v>15</v>
       </c>
-      <c r="H9" t="n">
+      <c r="M9" t="n">
         <v>11</v>
       </c>
-      <c r="I9" t="n">
+      <c r="N9" t="n">
         <v>16</v>
       </c>
-      <c r="J9" t="n">
+      <c r="O9" t="n">
         <v>16</v>
       </c>
-      <c r="K9" t="n">
+      <c r="P9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -801,21 +946,36 @@
         <v>28</v>
       </c>
       <c r="F10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" t="n">
         <v>16</v>
       </c>
-      <c r="G10" t="n">
+      <c r="L10" t="n">
         <v>18</v>
       </c>
-      <c r="H10" t="n">
+      <c r="M10" t="n">
         <v>30</v>
       </c>
-      <c r="I10" t="n">
+      <c r="N10" t="n">
         <v>40</v>
       </c>
-      <c r="J10" t="n">
+      <c r="O10" t="n">
         <v>42</v>
       </c>
-      <c r="K10" t="n">
+      <c r="P10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -838,21 +998,36 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
         <v>11</v>
       </c>
       <c r="I11" t="n">
+        <v>18</v>
+      </c>
+      <c r="J11" t="n">
+        <v>13</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="n">
         <v>17</v>
       </c>
-      <c r="J11" t="n">
+      <c r="O11" t="n">
         <v>16</v>
       </c>
-      <c r="K11" t="n">
+      <c r="P11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -875,21 +1050,36 @@
         <v>17</v>
       </c>
       <c r="F12" t="n">
+        <v>26</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K12" t="n">
         <v>19</v>
       </c>
-      <c r="G12" t="n">
+      <c r="L12" t="n">
         <v>16</v>
       </c>
-      <c r="H12" t="n">
+      <c r="M12" t="n">
         <v>15</v>
       </c>
-      <c r="I12" t="n">
+      <c r="N12" t="n">
         <v>17</v>
       </c>
-      <c r="J12" t="n">
+      <c r="O12" t="n">
         <v>7</v>
       </c>
-      <c r="K12" t="n">
+      <c r="P12" t="n">
         <v>20</v>
       </c>
     </row>
@@ -912,21 +1102,36 @@
         <v>36</v>
       </c>
       <c r="F13" t="n">
+        <v>18</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19</v>
+      </c>
+      <c r="H13" t="n">
+        <v>14</v>
+      </c>
+      <c r="I13" t="n">
+        <v>22</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" t="n">
         <v>13</v>
       </c>
-      <c r="G13" t="n">
+      <c r="L13" t="n">
         <v>23</v>
       </c>
-      <c r="H13" t="n">
+      <c r="M13" t="n">
         <v>25</v>
       </c>
-      <c r="I13" t="n">
+      <c r="N13" t="n">
         <v>25</v>
       </c>
-      <c r="J13" t="n">
+      <c r="O13" t="n">
         <v>18</v>
       </c>
-      <c r="K13" t="n">
+      <c r="P13" t="n">
         <v>15</v>
       </c>
     </row>
@@ -941,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,30 +1177,55 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1025,30 +1255,55 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1082,30 +1337,55 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1139,30 +1419,51 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1181,41 +1482,66 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1247,28 +1573,49 @@
           <t>20</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1300,28 +1647,53 @@
           <t>19</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1351,30 +1723,55 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1406,28 +1803,53 @@
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1461,30 +1883,51 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -1518,30 +1961,55 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1575,30 +2043,55 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1632,30 +2125,55 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>15</t>
         </is>

--- a/data/viviate.xlsx
+++ b/data/viviate.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,30 +482,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -545,10 +550,10 @@
         <v>15</v>
       </c>
       <c r="K2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L2" t="n">
         <v>14</v>
-      </c>
-      <c r="L2" t="n">
-        <v>21</v>
       </c>
       <c r="M2" t="n">
         <v>21</v>
@@ -557,11 +562,14 @@
         <v>21</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
         <v>20</v>
       </c>
+      <c r="Q2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -597,21 +605,24 @@
         <v>8</v>
       </c>
       <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
         <v>13</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>22</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>24</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>28</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>18</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>16</v>
       </c>
     </row>
@@ -649,21 +660,24 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" t="n">
         <v>12</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>22</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>23</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>26</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>18</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -701,21 +715,24 @@
         <v>10</v>
       </c>
       <c r="K5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L5" t="n">
         <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>17</v>
       </c>
       <c r="M5" t="n">
         <v>17</v>
       </c>
       <c r="N5" t="n">
+        <v>17</v>
+      </c>
+      <c r="O5" t="n">
         <v>12</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>10</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -753,21 +770,24 @@
         <v>30</v>
       </c>
       <c r="K6" t="n">
+        <v>13</v>
+      </c>
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>16</v>
-      </c>
-      <c r="M6" t="n">
-        <v>14</v>
       </c>
       <c r="N6" t="n">
         <v>14</v>
       </c>
       <c r="O6" t="n">
+        <v>14</v>
+      </c>
+      <c r="P6" t="n">
         <v>11</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>9</v>
       </c>
     </row>
@@ -805,21 +825,24 @@
         <v>25</v>
       </c>
       <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>15</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>12</v>
-      </c>
-      <c r="N7" t="n">
-        <v>13</v>
       </c>
       <c r="O7" t="n">
         <v>13</v>
       </c>
       <c r="P7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -857,23 +880,26 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
+        <v>9</v>
+      </c>
+      <c r="L8" t="n">
         <v>10</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>20</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>13</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>14</v>
-      </c>
-      <c r="O8" t="n">
-        <v>10</v>
       </c>
       <c r="P8" t="n">
         <v>10</v>
       </c>
+      <c r="Q8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -909,21 +935,24 @@
         <v>13</v>
       </c>
       <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>15</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>11</v>
-      </c>
-      <c r="N9" t="n">
-        <v>16</v>
       </c>
       <c r="O9" t="n">
         <v>16</v>
       </c>
       <c r="P9" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -961,21 +990,24 @@
         <v>24</v>
       </c>
       <c r="K10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" t="n">
         <v>16</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>18</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>30</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>40</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>42</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -1013,21 +1045,24 @@
         <v>13</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>15</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>17</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>16</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1065,21 +1100,24 @@
         <v>25</v>
       </c>
       <c r="K12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" t="n">
         <v>19</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>16</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>15</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>17</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>7</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1117,21 +1155,24 @@
         <v>7</v>
       </c>
       <c r="K13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" t="n">
         <v>13</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>23</v>
-      </c>
-      <c r="M13" t="n">
-        <v>25</v>
       </c>
       <c r="N13" t="n">
         <v>25</v>
       </c>
       <c r="O13" t="n">
+        <v>25</v>
+      </c>
+      <c r="P13" t="n">
         <v>18</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1146,7 +1187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1202,30 +1243,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1280,30 +1326,35 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1362,30 +1413,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1440,30 +1496,35 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1520,28 +1581,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1594,28 +1660,33 @@
           <t>30</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1672,28 +1743,33 @@
           <t>25</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1748,30 +1824,35 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1828,28 +1909,33 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1904,30 +1990,35 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -1984,32 +2075,33 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2068,30 +2160,35 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -2150,30 +2247,35 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>15</t>
         </is>

--- a/data/viviate.xlsx
+++ b/data/viviate.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,30 +487,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -553,10 +558,10 @@
         <v>18</v>
       </c>
       <c r="L2" t="n">
+        <v>25</v>
+      </c>
+      <c r="M2" t="n">
         <v>14</v>
-      </c>
-      <c r="M2" t="n">
-        <v>21</v>
       </c>
       <c r="N2" t="n">
         <v>21</v>
@@ -565,11 +570,14 @@
         <v>21</v>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="n">
         <v>20</v>
       </c>
+      <c r="R2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -608,21 +616,24 @@
         <v>6</v>
       </c>
       <c r="L3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" t="n">
         <v>13</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>22</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>24</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>28</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>18</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>16</v>
       </c>
     </row>
@@ -663,21 +674,24 @@
         <v>7</v>
       </c>
       <c r="L4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" t="n">
         <v>12</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>22</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>23</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>26</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>18</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -718,21 +732,24 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M5" t="n">
         <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>17</v>
       </c>
       <c r="N5" t="n">
         <v>17</v>
       </c>
       <c r="O5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P5" t="n">
         <v>12</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>10</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -773,21 +790,24 @@
         <v>13</v>
       </c>
       <c r="L6" t="n">
+        <v>18</v>
+      </c>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>16</v>
-      </c>
-      <c r="N6" t="n">
-        <v>14</v>
       </c>
       <c r="O6" t="n">
         <v>14</v>
       </c>
       <c r="P6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q6" t="n">
         <v>11</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>9</v>
       </c>
     </row>
@@ -828,21 +848,24 @@
         <v>10</v>
       </c>
       <c r="L7" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>15</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>12</v>
-      </c>
-      <c r="O7" t="n">
-        <v>13</v>
       </c>
       <c r="P7" t="n">
         <v>13</v>
       </c>
       <c r="Q7" t="n">
+        <v>13</v>
+      </c>
+      <c r="R7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -883,23 +906,26 @@
         <v>9</v>
       </c>
       <c r="L8" t="n">
+        <v>12</v>
+      </c>
+      <c r="M8" t="n">
         <v>10</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>20</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>13</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>14</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
       </c>
       <c r="Q8" t="n">
         <v>10</v>
       </c>
+      <c r="R8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -938,21 +964,24 @@
         <v>4</v>
       </c>
       <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>15</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>11</v>
-      </c>
-      <c r="O9" t="n">
-        <v>16</v>
       </c>
       <c r="P9" t="n">
         <v>16</v>
       </c>
       <c r="Q9" t="n">
+        <v>16</v>
+      </c>
+      <c r="R9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -993,21 +1022,24 @@
         <v>20</v>
       </c>
       <c r="L10" t="n">
+        <v>27</v>
+      </c>
+      <c r="M10" t="n">
         <v>16</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>18</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>30</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>40</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>42</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -1048,21 +1080,24 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M11" t="n">
         <v>4</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>15</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>11</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>17</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>16</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1103,21 +1138,24 @@
         <v>10</v>
       </c>
       <c r="L12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M12" t="n">
         <v>19</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>16</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>15</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>17</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>7</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1158,21 +1196,24 @@
         <v>7</v>
       </c>
       <c r="L13" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" t="n">
         <v>13</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>23</v>
-      </c>
-      <c r="N13" t="n">
-        <v>25</v>
       </c>
       <c r="O13" t="n">
         <v>25</v>
       </c>
       <c r="P13" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q13" t="n">
         <v>18</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1187,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,30 +1289,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1331,30 +1377,35 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1418,30 +1469,35 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1501,30 +1557,35 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1586,28 +1647,33 @@
           <t>11</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1665,28 +1731,33 @@
           <t>13</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1748,28 +1819,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1829,30 +1905,35 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1914,28 +1995,33 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1995,30 +2081,35 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -2078,30 +2169,35 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2165,30 +2261,35 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -2252,30 +2353,35 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>15</t>
         </is>

--- a/data/viviate.xlsx
+++ b/data/viviate.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,30 +492,45 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -561,21 +576,30 @@
         <v>25</v>
       </c>
       <c r="M2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O2" t="n">
         <v>14</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q2" t="n">
         <v>21</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>21</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>21</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>20</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>20</v>
       </c>
     </row>
@@ -619,21 +643,30 @@
         <v>8</v>
       </c>
       <c r="M3" t="n">
+        <v>15</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="n">
         <v>13</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>22</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>24</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>28</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>18</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>16</v>
       </c>
     </row>
@@ -677,21 +710,30 @@
         <v>6</v>
       </c>
       <c r="M4" t="n">
+        <v>14</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
         <v>12</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>22</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>23</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>26</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>18</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -735,21 +777,30 @@
         <v>13</v>
       </c>
       <c r="M5" t="n">
+        <v>14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>14</v>
+      </c>
+      <c r="O5" t="n">
+        <v>16</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>17</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>17</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>12</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -793,21 +844,30 @@
         <v>18</v>
       </c>
       <c r="M6" t="n">
+        <v>12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>16</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>14</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>9</v>
       </c>
     </row>
@@ -824,7 +884,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
         <v>19</v>
@@ -851,21 +911,30 @@
         <v>12</v>
       </c>
       <c r="M7" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>15</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>12</v>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>13</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>13</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -909,21 +978,30 @@
         <v>12</v>
       </c>
       <c r="M8" t="n">
+        <v>9</v>
+      </c>
+      <c r="N8" t="n">
         <v>10</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
         <v>20</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>13</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>14</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>10</v>
       </c>
     </row>
@@ -967,21 +1045,30 @@
         <v>8</v>
       </c>
       <c r="M9" t="n">
+        <v>20</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>15</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>11</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>16</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>16</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1025,21 +1112,30 @@
         <v>27</v>
       </c>
       <c r="M10" t="n">
+        <v>28</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14</v>
+      </c>
+      <c r="O10" t="n">
+        <v>21</v>
+      </c>
+      <c r="P10" t="n">
         <v>16</v>
       </c>
-      <c r="N10" t="n">
+      <c r="Q10" t="n">
         <v>18</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>30</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>40</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
         <v>42</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -1083,21 +1179,30 @@
         <v>8</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" t="n">
         <v>4</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>15</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
         <v>11</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>17</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>16</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1141,21 +1246,30 @@
         <v>14</v>
       </c>
       <c r="M12" t="n">
+        <v>13</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
         <v>19</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>16</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>15</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>17</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>7</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1199,21 +1313,30 @@
         <v>7</v>
       </c>
       <c r="M13" t="n">
+        <v>15</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
         <v>23</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>25</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>25</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>18</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1228,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1294,30 +1417,45 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1382,30 +1520,45 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1474,30 +1627,45 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1562,30 +1730,45 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1652,28 +1835,43 @@
           <t>13</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1736,28 +1934,43 @@
           <t>18</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1781,71 +1994,86 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1910,30 +2138,45 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2000,28 +2243,43 @@
           <t>8</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2086,30 +2344,45 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -2172,32 +2445,43 @@
           <t>8</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2266,30 +2550,45 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -2358,30 +2657,45 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>15</t>
         </is>

--- a/data/viviate.xlsx
+++ b/data/viviate.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,30 +507,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -585,10 +590,10 @@
         <v>14</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>14</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>21</v>
       </c>
       <c r="R2" t="n">
         <v>21</v>
@@ -597,9 +602,12 @@
         <v>21</v>
       </c>
       <c r="T2" t="n">
+        <v>21</v>
+      </c>
+      <c r="U2" t="n">
         <v>20</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>20</v>
       </c>
     </row>
@@ -652,21 +660,24 @@
         <v>5</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>13</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>22</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>24</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>28</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>18</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>16</v>
       </c>
     </row>
@@ -719,21 +730,24 @@
         <v>4</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>12</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>22</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>23</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>26</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>18</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -789,18 +803,21 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>17</v>
       </c>
       <c r="S5" t="n">
+        <v>17</v>
+      </c>
+      <c r="T5" t="n">
         <v>12</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>10</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -853,21 +870,24 @@
         <v>10</v>
       </c>
       <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>16</v>
-      </c>
-      <c r="R6" t="n">
-        <v>14</v>
       </c>
       <c r="S6" t="n">
         <v>14</v>
       </c>
       <c r="T6" t="n">
+        <v>14</v>
+      </c>
+      <c r="U6" t="n">
         <v>11</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>9</v>
       </c>
     </row>
@@ -920,21 +940,24 @@
         <v>5</v>
       </c>
       <c r="P7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>15</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>12</v>
-      </c>
-      <c r="S7" t="n">
-        <v>13</v>
       </c>
       <c r="T7" t="n">
         <v>13</v>
       </c>
       <c r="U7" t="n">
+        <v>13</v>
+      </c>
+      <c r="V7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -987,21 +1010,24 @@
         <v>10</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>10</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>20</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>13</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>14</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>10</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1054,21 +1080,24 @@
         <v>10</v>
       </c>
       <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>15</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>11</v>
-      </c>
-      <c r="S9" t="n">
-        <v>16</v>
       </c>
       <c r="T9" t="n">
         <v>16</v>
       </c>
       <c r="U9" t="n">
+        <v>16</v>
+      </c>
+      <c r="V9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1121,21 +1150,24 @@
         <v>21</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>16</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>18</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>30</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>40</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>42</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -1188,21 +1220,24 @@
         <v>7</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>15</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>11</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>17</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>16</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1255,21 +1290,24 @@
         <v>5</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>19</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>16</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>15</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>17</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>7</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1322,21 +1360,24 @@
         <v>5</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>13</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>23</v>
-      </c>
-      <c r="R13" t="n">
-        <v>25</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
       </c>
       <c r="T13" t="n">
+        <v>25</v>
+      </c>
+      <c r="U13" t="n">
         <v>18</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1351,7 +1392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1432,30 +1473,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1533,32 +1579,33 @@
           <t>14</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1640,32 +1687,33 @@
           <t>5</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1743,32 +1791,33 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1851,27 +1900,28 @@
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1949,28 +1999,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2052,28 +2107,33 @@
           <t>5</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2151,32 +2211,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2258,28 +2319,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2357,32 +2423,33 @@
           <t>21</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -2456,32 +2523,33 @@
           <t>7</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2563,32 +2631,33 @@
           <t>5</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -2670,32 +2739,33 @@
           <t>5</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
